--- a/01_Raw_data/stream slopes.xlsx
+++ b/01_Raw_data/stream slopes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Howley_Bradford_Streams\Howley_Bradford_Streams\01_Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF907974-5C42-4881-AF78-43C82274F6AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0487FD-2D9C-49E2-8601-8044308BEC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="19185" windowHeight="10065" activeTab="1" xr2:uid="{B0316C70-1A91-4503-8B34-202AE1CBC864}"/>
+    <workbookView xWindow="-40" yWindow="-40" windowWidth="19280" windowHeight="10160" xr2:uid="{B0316C70-1A91-4503-8B34-202AE1CBC864}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -162,10 +162,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -907,160 +906,158 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7326EEA6-98D1-4DE2-AFC8-D17447EC27A5}">
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A2" s="2">
+      <c r="A2">
         <v>9</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>129.08000000000001</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>3.5399999999999991</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>2.1549999999999998</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2">
         <v>2.742485280446234E-2</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A3" s="2">
+      <c r="A3">
         <v>5</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>68.69</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>5.9620000000000033</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>0.47450000000000003</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3">
         <v>8.6795749017324259E-2</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>45.21</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4">
         <v>12.216000000000001</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4">
         <v>2.11</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4">
         <v>0.27020570670205707</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A5" s="2">
+      <c r="A5">
         <v>15</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>67.73</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5">
         <v>5.1430000000000007</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>1.9750000000000001</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5">
         <v>7.5933855012549831E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A6" s="2">
+      <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>59.95</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
         <v>0.6390000000000029</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>1.1145</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <v>1.0658882402001716E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A7" s="2">
+      <c r="A7">
         <v>7</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7">
         <v>51.1</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7">
         <v>0.44500000000000028</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
         <v>8.7084148727984406E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A8" s="2">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>144.53</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8">
         <v>0.12599999999999767</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8">
         <v>0.22499999999999998</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
         <v>8.7179132360062038E-4</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A9" s="2">
+      <c r="A9">
         <v>13</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.75">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
